--- a/assets/data/goodsList.xlsx
+++ b/assets/data/goodsList.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
-    <sheet name="球迷好物数据表" sheetId="2" r:id="rId1"/>
+    <sheet name="Fan Goods Data" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,405 +26,8 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="132">
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>一级分类</t>
-  </si>
-  <si>
-    <t>二级分类</t>
-  </si>
-  <si>
-    <t>商品名称</t>
-  </si>
-  <si>
-    <t>适用运动</t>
-  </si>
-  <si>
-    <t>球队/球星</t>
-  </si>
-  <si>
-    <t>品牌</t>
-  </si>
-  <si>
-    <t>规格/材质</t>
-  </si>
-  <si>
-    <t>参考价格(元)</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>配图URL</t>
-  </si>
-  <si>
-    <t>球衣装备库</t>
-  </si>
-  <si>
-    <t>球队主客场球衣</t>
-  </si>
-  <si>
-    <t>皇马 2024-25 主场球衣</t>
-  </si>
-  <si>
-    <t>足球</t>
-  </si>
-  <si>
-    <t>皇家马德里</t>
-  </si>
-  <si>
-    <t>Adidas</t>
-  </si>
-  <si>
-    <t>球迷版/棉涤混纺</t>
-  </si>
-  <si>
-    <t>想入手</t>
-  </si>
-  <si>
-    <t>印号可选</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/56lx7sUHHl</t>
-  </si>
-  <si>
-    <t>皇马 2024-25 客场球衣</t>
-  </si>
-  <si>
-    <t>球迷版</t>
-  </si>
-  <si>
-    <t>观望</t>
-  </si>
-  <si>
-    <t>紫色款</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/2udbNcpCZy</t>
-  </si>
-  <si>
-    <t>曼城 2024-25 主场球衣</t>
-  </si>
-  <si>
-    <t>曼城</t>
-  </si>
-  <si>
-    <t>Puma</t>
-  </si>
-  <si>
-    <t>天蓝色</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/CIeljLhncY</t>
-  </si>
-  <si>
-    <t>复古球衣</t>
-  </si>
-  <si>
-    <t>阿根廷 2022世界杯 复古球衣</t>
-  </si>
-  <si>
-    <t>阿根廷</t>
-  </si>
-  <si>
-    <t>球员收藏版</t>
-  </si>
-  <si>
-    <t>三星徽章</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/E6XUxrEij6</t>
-  </si>
-  <si>
-    <t>巴西 2022 复古球衣</t>
-  </si>
-  <si>
-    <t>巴西</t>
-  </si>
-  <si>
-    <t>Nike</t>
-  </si>
-  <si>
-    <t>已拥有</t>
-  </si>
-  <si>
-    <t>黄绿经典</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/hQ01ZpIxzR</t>
-  </si>
-  <si>
-    <t>球员专属球衣</t>
-  </si>
-  <si>
-    <t>梅西 阿根廷 10号签名球衣</t>
-  </si>
-  <si>
-    <t>阿根廷(梅西)</t>
-  </si>
-  <si>
-    <t>球员版签名</t>
-  </si>
-  <si>
-    <t>限量签名</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/FrBKvOUJbO</t>
-  </si>
-  <si>
-    <t>库里 勇士 30号签名球衣</t>
-  </si>
-  <si>
-    <t>篮球</t>
-  </si>
-  <si>
-    <t>金州勇士(库里)</t>
-  </si>
-  <si>
-    <t>Under Armour</t>
-  </si>
-  <si>
-    <t>印花款</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/Jupm5ylHv0</t>
-  </si>
-  <si>
-    <t>城市版球衣</t>
-  </si>
-  <si>
-    <t>湖人 城市版球衣</t>
-  </si>
-  <si>
-    <t>洛杉矶湖人</t>
-  </si>
-  <si>
-    <t>限定配色</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/FcD5CU3ffU</t>
-  </si>
-  <si>
-    <t>勇士 城市版球衣</t>
-  </si>
-  <si>
-    <t>金州勇士</t>
-  </si>
-  <si>
-    <t>湾区限定</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/SQKQsUBCRj</t>
-  </si>
-  <si>
-    <t>球星球鞋库</t>
-  </si>
-  <si>
-    <t>足球战靴</t>
-  </si>
-  <si>
-    <t>耐克 刺客15 足球战靴</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Mercurial Superfly FG</t>
-  </si>
-  <si>
-    <t>速度型</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/5wPZd9PkvS</t>
-  </si>
-  <si>
-    <t>Adidas 猎鹰 Predator Elite 足球鞋</t>
-  </si>
-  <si>
-    <t>Predator Elite FG</t>
-  </si>
-  <si>
-    <t>掌控型</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/uBFVL57opu</t>
-  </si>
-  <si>
-    <t>篮球球星签名鞋</t>
-  </si>
-  <si>
-    <t>库里 Curry 12 篮球签名鞋</t>
-  </si>
-  <si>
-    <t>库里(Under Armour)</t>
-  </si>
-  <si>
-    <t>实战签名款</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/ctL3cV1DkQ</t>
-  </si>
-  <si>
-    <t>詹姆斯 Nike LeBron 21 篮球签名鞋</t>
-  </si>
-  <si>
-    <t>詹姆斯(湖人)</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/17xvccOWcW</t>
-  </si>
-  <si>
-    <t>乔丹 Air Jordan 1 篮球鞋</t>
-  </si>
-  <si>
-    <t>迈克尔·乔丹</t>
-  </si>
-  <si>
-    <t>经典复刻</t>
-  </si>
-  <si>
-    <t>收藏款</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/kOVuntVN5v</t>
-  </si>
-  <si>
-    <t>球迷文创周边</t>
-  </si>
-  <si>
-    <t>队徽钥匙扣</t>
-  </si>
-  <si>
-    <t>皇马 队徽钥匙扣</t>
-  </si>
-  <si>
-    <t>金属烤漆</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/eOmTQD62X9</t>
-  </si>
-  <si>
-    <t>抱枕</t>
-  </si>
-  <si>
-    <t>曼城 主题抱枕</t>
-  </si>
-  <si>
-    <t>绒面/填充棉</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/NvCfZOLGp5</t>
-  </si>
-  <si>
-    <t>海报</t>
-  </si>
-  <si>
-    <t>梅西 经典庆祝海报</t>
-  </si>
-  <si>
-    <t>梅西</t>
-  </si>
-  <si>
-    <t>铜版纸/高清</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/gBfXD0UstD</t>
-  </si>
-  <si>
-    <t>手办</t>
-  </si>
-  <si>
-    <t>C罗 标志性庆祝手办</t>
-  </si>
-  <si>
-    <t>C罗</t>
-  </si>
-  <si>
-    <t>PVC/12cm</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/n4idxJuvUs</t>
-  </si>
-  <si>
-    <t>球星卡</t>
-  </si>
-  <si>
-    <t>梅西 球星卡</t>
-  </si>
-  <si>
-    <t>评级卡(PSA)</t>
-  </si>
-  <si>
-    <t>收藏卡</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/o3NBs1WykR</t>
-  </si>
-  <si>
-    <t>赛事纪念徽章</t>
-  </si>
-  <si>
-    <t>欧冠 纪念徽章</t>
-  </si>
-  <si>
-    <t>欧冠</t>
-  </si>
-  <si>
-    <t>合金</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/sEEooojJ7N</t>
-  </si>
-  <si>
-    <t>限定周边</t>
-  </si>
-  <si>
-    <t>世界杯 限定周边套装</t>
-  </si>
-  <si>
-    <t>世界杯</t>
-  </si>
-  <si>
-    <t>多材质</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/0Euk4EJXcA</t>
-  </si>
-  <si>
-    <t>生活周边</t>
-  </si>
-  <si>
-    <t>球队 定制手机壳</t>
-  </si>
-  <si>
-    <t>足球/篮球</t>
-  </si>
-  <si>
-    <t>自定义</t>
-  </si>
-  <si>
-    <t>硅胶/硬壳</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/lFA9mdVFVH</t>
-  </si>
-  <si>
-    <t>球队 壁纸挂饰</t>
-  </si>
-  <si>
-    <t>布艺/树脂</t>
-  </si>
-  <si>
-    <t>https://aka.doubaocdn.com/s/ZBY6XjYtMp</t>
-  </si>
-</sst>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="132"><si><t>Index</t></si><si><t>Category</t></si><si><t>Subcategory</t></si><si><t>Product Name</t></si><si><t>Sport</t></si><si><t>Team/Star</t></si><si><t>Brand</t></si><si><t>Spec/Material</t></si><si><t>Ref Price (CNY)</t></si><si><t>Status</t></si><si><t>Remark</t></si><si><t>Image URL</t></si><si><t>Jersey Collection</t></si><si><t>Home & Away Jerseys</t></si><si><t>Real Madrid 2024-25 Home Jersey</t></si><si><t>Football</t></si><si><t>Real Madrid</t></si><si><t>Adidas</t></si><si><t>Fan Version / Cotton-Poly Blend</t></si><si><t>Want</t></si><si><t>Optional Printing</t></si><si><t>https://aka.doubaocdn.com/s/56lx7sUHHl</t></si><si><t>Real Madrid 2024-25 Away Jersey</t></si><si><t>Fan Version</t></si><si><t>Watching</t></si><si><t>Purple Edition</t></si><si><t>https://aka.doubaocdn.com/s/2udbNcpCZy</t></si><si><t>Man City 2024-25 Home Jersey</t></si><si><t>Man City</t></si><si><t>Puma</t></si><si><t>Sky Blue</t></si><si><t>https://aka.doubaocdn.com/s/CIeljLhncY</t></si><si><t>Retro Jerseys</t></si><si><t>Argentina 2022 World Cup Retro Jersey</t></si><si><t>Argentina</t></si><si><t>Player Collector Edition</t></si><si><t>Three-Star Badge</t></si><si><t>https://aka.doubaocdn.com/s/E6XUxrEij6</t></si><si><t>Brazil 2022 Retro Jersey</t></si><si><t>Brazil</t></si><si><t>Nike</t></si><si><t>Owned</t></si><si><t>Classic Yellow-Green</t></si><si><t>https://aka.doubaocdn.com/s/hQ01ZpIxzR</t></si><si><t>Player Signature Jerseys</t></si><si><t>Messi Argentina #10 Signed Jersey</t></si><si><t>Argentina (Messi)</t></si><si><t>Player Signed Version</t></si><si><t>Limited Signature</t></si><si><t>https://aka.doubaocdn.com/s/FrBKvOUJbO</t></si><si><t>Curry Warriors #30 Signed Jersey</t></si><si><t>Basketball</t></si><si><t>Warriors (Curry)</t></si><si><t>Under Armour</t></si><si><t>Print Edition</t></si><si><t>https://aka.doubaocdn.com/s/Jupm5ylHv0</t></si><si><t>City Edition Jerseys</t></si><si><t>Lakers City Edition Jersey</t></si><si><t>LA Lakers</t></si><si><t>Limited Colorway</t></si><si><t>https://aka.doubaocdn.com/s/FcD5CU3ffU</t></si><si><t>Warriors City Edition Jersey</t></si><si><t>Warriors</t></si><si><t>Bay Area Limited</t></si><si><t>https://aka.doubaocdn.com/s/SQKQsUBCRj</t></si><si><t>Star Boots Collection</t></si><si><t>Football Boots</t></si><si><t>Nike Mercurial 15 Football Boots</t></si><si><t>-</t></si><si><t>Mercurial Superfly FG</t></si><si><t>Speed Type</t></si><si><t>https://aka.doubaocdn.com/s/5wPZd9PkvS</t></si><si><t>Adidas Predator Elite Football Boots</t></si><si><t>Predator Elite FG</t></si><si><t>Control Type</t></si><si><t>https://aka.doubaocdn.com/s/uBFVL57opu</t></si><si><t>Basketball Signature Shoes</t></si><si><t>Curry 12 Basketball Signature Shoes</t></si><si><t>Curry (Under Armour)</t></si><si><t>Game Signature</t></si><si><t>https://aka.doubaocdn.com/s/ctL3cV1DkQ</t></si><si><t>Nike LeBron 21 Basketball Signature Shoes</t></si><si><t>LeBron (Lakers)</t></si><si><t>https://aka.doubaocdn.com/s/17xvccOWcW</t></si><si><t>Air Jordan 1 Basketball Shoes</t></si><si><t>Michael Jordan</t></si><si><t>Classic Retro</t></si><si><t>Collector Edition</t></si><si><t>https://aka.doubaocdn.com/s/kOVuntVN5v</t></si><si><t>Creative Merchandise</t></si><si><t>Crest Keychains</t></si><si><t>Real Madrid Crest Keychain</t></si><si><t>Metal Lacquered</t></si><si><t>https://aka.doubaocdn.com/s/eOmTQD62X9</t></si><si><t>Cushions</t></si><si><t>Man City Theme Cushion</t></si><si><t>Plush / Cotton Fill</t></si><si><t>https://aka.doubaocdn.com/s/NvCfZOLGp5</t></si><si><t>Posters</t></si><si><t>Messi Classic Celebration Poster</t></si><si><t>Messi</t></si><si><t>Coated Paper / HD</t></si><si><t>https://aka.doubaocdn.com/s/gBfXD0UstD</t></si><si><t>Figurines</t></si><si><t>Ronaldo Signature Celebration Figurine</t></si><si><t>Ronaldo</t></si><si><t>PVC/12cm</t></si><si><t>https://aka.doubaocdn.com/s/n4idxJuvUs</t></si><si><t>Player Cards</t></si><si><t>Messi Player Card</t></si><si><t>Graded Card (PSA)</t></si><si><t>Collectible Card</t></si><si><t>https://aka.doubaocdn.com/s/o3NBs1WykR</t></si><si><t>Commemorative Badges</t></si><si><t>UCL Commemorative Badge</t></si><si><t>UCL</t></si><si><t>Alloy</t></si><si><t>https://aka.doubaocdn.com/s/sEEooojJ7N</t></si><si><t>Limited Edition</t></si><si><t>World Cup Limited Edition Set</t></si><si><t>World Cup</t></si><si><t>Multi-Material</t></si><si><t>https://aka.doubaocdn.com/s/0Euk4EJXcA</t></si><si><t>Lifestyle Merchandise</t></si><si><t>Team Custom Phone Case</t></si><si><t>Football/Basketball</t></si><si><t>Customizable</t></si><si><t>Silicone / Hard Shell</t></si><si><t>https://aka.doubaocdn.com/s/lFA9mdVFVH</t></si><si><t>Team Wall Hanging</t></si><si><t>Fabric / Resin</t></si><si><t>https://aka.doubaocdn.com/s/ZBY6XjYtMp</t></si></sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,7 +42,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -447,14 +50,14 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -462,14 +65,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -477,14 +80,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -492,7 +95,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -500,7 +103,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -508,7 +111,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -516,7 +119,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -524,14 +127,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -539,7 +142,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -547,7 +150,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -555,14 +158,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -570,42 +173,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -1103,55 +706,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Thousands Separator" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Thousands Separator[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Heading" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Moderate" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent 1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent 2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent 3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent 4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent 5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1249,10 +852,10 @@
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="Yu Gothic Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="DengXian Light"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1284,10 +887,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="DengXian"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
